--- a/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
@@ -429,27 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>B3_Q</t>
+          <t>B3_Q_per_turn</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>B4_SR</t>
+          <t>B4_SR_per_turn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>B5_CR</t>
+          <t>B5_CR_per_turn</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>B6_AF</t>
+          <t>B6_AF_per_turn</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>B2_Persuade</t>
+          <t>B2_Persuade_per_turn</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -483,19 +483,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6.552</v>
+        <v>0.471</v>
       </c>
       <c r="D2" t="n">
-        <v>2.896</v>
+        <v>0.199</v>
       </c>
       <c r="E2" t="n">
-        <v>1.292</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.417</v>
+        <v>0.026</v>
       </c>
       <c r="G2" t="n">
-        <v>1.042</v>
+        <v>0.078</v>
       </c>
       <c r="H2" t="n">
         <v>0.765</v>
@@ -520,19 +520,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6.125</v>
+        <v>0.461</v>
       </c>
       <c r="D3" t="n">
-        <v>2.49</v>
+        <v>0.152</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26</v>
+        <v>0.073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.438</v>
+        <v>0.023</v>
       </c>
       <c r="G3" t="n">
-        <v>1.333</v>
+        <v>0.101</v>
       </c>
       <c r="H3" t="n">
         <v>0.656</v>
@@ -557,19 +557,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>7.229</v>
+        <v>0.476</v>
       </c>
       <c r="D4" t="n">
-        <v>2.719</v>
+        <v>0.175</v>
       </c>
       <c r="E4" t="n">
-        <v>1.312</v>
+        <v>0.078</v>
       </c>
       <c r="F4" t="n">
-        <v>0.542</v>
+        <v>0.029</v>
       </c>
       <c r="G4" t="n">
-        <v>1.281</v>
+        <v>0.091</v>
       </c>
       <c r="H4" t="n">
         <v>0.728</v>
@@ -594,19 +594,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.01</v>
+        <v>0.486</v>
       </c>
       <c r="D5" t="n">
-        <v>2.635</v>
+        <v>0.179</v>
       </c>
       <c r="E5" t="n">
-        <v>1.26</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.354</v>
+        <v>0.023</v>
       </c>
       <c r="G5" t="n">
-        <v>1.094</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0.626</v>
@@ -631,19 +631,19 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>5.271</v>
+        <v>0.423</v>
       </c>
       <c r="D6" t="n">
-        <v>2.615</v>
+        <v>0.184</v>
       </c>
       <c r="E6" t="n">
-        <v>1.427</v>
+        <v>0.097</v>
       </c>
       <c r="F6" t="n">
-        <v>0.49</v>
+        <v>0.031</v>
       </c>
       <c r="G6" t="n">
-        <v>1.635</v>
+        <v>0.118</v>
       </c>
       <c r="H6" t="n">
         <v>0.764</v>
@@ -668,19 +668,19 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5.062</v>
+        <v>0.454</v>
       </c>
       <c r="D7" t="n">
-        <v>2.396</v>
+        <v>0.161</v>
       </c>
       <c r="E7" t="n">
-        <v>1.396</v>
+        <v>0.092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.479</v>
+        <v>0.026</v>
       </c>
       <c r="G7" t="n">
-        <v>1.615</v>
+        <v>0.123</v>
       </c>
       <c r="H7" t="n">
         <v>0.6820000000000001</v>
@@ -705,19 +705,19 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4.49</v>
+        <v>0.444</v>
       </c>
       <c r="D8" t="n">
-        <v>1.875</v>
+        <v>0.137</v>
       </c>
       <c r="E8" t="n">
-        <v>1.021</v>
+        <v>0.078</v>
       </c>
       <c r="F8" t="n">
-        <v>0.51</v>
+        <v>0.032</v>
       </c>
       <c r="G8" t="n">
-        <v>1.677</v>
+        <v>0.144</v>
       </c>
       <c r="H8" t="n">
         <v>0.589</v>

--- a/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="behavior_by_iter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mici_behavior_by_iter" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pct_patient_by_iter" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +456,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>B1_GI_per_turn</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>B7_Seek_per_turn</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>RtoQ</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Empathy</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>loop</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>q_per_turn</t>
         </is>
@@ -498,15 +510,21 @@
         <v>0.078</v>
       </c>
       <c r="H2" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.765</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>3.458</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -535,15 +553,21 @@
         <v>0.101</v>
       </c>
       <c r="H3" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.656</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>3.646</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.354</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.884</v>
       </c>
     </row>
@@ -572,15 +596,21 @@
         <v>0.091</v>
       </c>
       <c r="H4" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.728</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3.448</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.448</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.766</v>
       </c>
     </row>
@@ -609,15 +639,21 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="H5" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.626</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>3.51</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.427</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.767</v>
       </c>
     </row>
@@ -646,15 +682,21 @@
         <v>0.118</v>
       </c>
       <c r="H6" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.764</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>3.74</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.417</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.779</v>
       </c>
     </row>
@@ -683,15 +725,21 @@
         <v>0.123</v>
       </c>
       <c r="H7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.6820000000000001</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>3.938</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.219</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.823</v>
       </c>
     </row>
@@ -720,16 +768,630 @@
         <v>0.144</v>
       </c>
       <c r="H8" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.589</v>
       </c>
+      <c r="K8" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.766</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MICI_Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MICI_Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MICI_Confront_rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MICI_AdviseNoPermission_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MICI_Warn_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MICI_Direct_rate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>MICI_Judge_rate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MICI_OverPraise_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.063</v>
+      </c>
       <c r="I8" t="n">
-        <v>4.146</v>
+        <v>0.003</v>
       </c>
       <c r="J8" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.766</v>
+        <v>0.043</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PCT_Importance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PCT_Confidence</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PCT_Readiness</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PCT_GlobalMean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PCT_ChangeProp</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PCT_ChangeTalk_prop</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PCT_SustainTalk_prop</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PCT_Neutral_prop</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.323</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.147</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.479</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.127</v>
       </c>
     </row>
   </sheetData>

--- a/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L5/tables/3_mechanism/3_mechanism.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="behavior_by_iter" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mici_behavior_by_iter" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pct_patient_by_iter" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="miti_threshold_verdicts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="q2_item_deltas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1397,4 +1399,1322 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reflection:Question (MITI)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>% Complex Reflections (MITI)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Technical global (MITI)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Relational global (MITI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO (K=5)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.77 ✗</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.28 ✗</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.94 ✗</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3.30 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO (K=5)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>final (iter 1)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.66 ✗</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.30 ✗</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.05 ✓fair</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3.55 ✓fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PTO (K=5)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.73 ✗</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.29 ✗</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.95 ✗</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3.34 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PTO (K=5)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>final (iter 4)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.59 ✗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.32 ✗</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.53 ✓fair</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4.08 ✓good</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>final_iter</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.448</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.552</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.385</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.302</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.323</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.271</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.562</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.104</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.958</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.958</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.906</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.344</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.271</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.073</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.771</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>